--- a/extenbooks/S302_extenbook.xlsx
+++ b/extenbooks/S302_extenbook.xlsx
@@ -4406,7 +4406,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -5362,11 +5362,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5389,88 +5389,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Expenditure Share of Necessaries, Case I</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S302_research.json", "adequacy_report": "Technical/docs/chapters/CH3_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S302_DPR.md", "epr": "Technical/docs/series/S302_EPR.md", "loader": "Technical/code/L01_loaders/L01_S302_load.py", "processor": "Technical/code/P02_processors/P02_S302_construct.py", "validator": "Technical/code/V03_validators/V03_S302_validate.py", "processed": "Technical/data/processed/S302.parquet", "chopped_csv": "Technical/chopped/S302.csv", "extenbook_xlsx": "Technical/extenbooks/S302_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S302-A"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["SHAIKH_2016_EQ_3_4_3_11"]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S302_extenbook.xlsx
+++ b/extenbooks/S302_extenbook.xlsx
@@ -4353,7 +4353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A114"/>
+  <dimension ref="A1:A119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4392,7 +4392,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Record type**: Data Provenance Record</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4427,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-wave-a-ch3 (Phase 5-8 fanout)</t>
+          <t>**Prepared by**: RSCD data-construction pipeline</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>- Research dossier: `Technical/research/S302_research.json`</t>
+          <t>- Series research notes: `Technical/research/S302_research.json`</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>## From the Book</t>
         </is>
       </c>
     </row>
@@ -4532,62 +4532,58 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+          <t>&gt; It is evident that the expenditure share on necessities declines as income increases, while that of luxuries rises.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>|---|---|---|---|---|</t>
+          <t>&gt; -- Shaikh (2016), Chapter 3, p. 93 &lt;!-- kb: ch03, p.93 (ch03_micro_foundations.md, expenditure-share result) --&gt;</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>| **S302-A** | n/a (theoretical) | Shaikh 2016 eq (3.11), p. 93; Figure 3.4 axis bounds p. 94 | dimensionless | analytic regeneration from equation |</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>## 3. Sources</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>## 4. Construction</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1. Income grid y in [1.0, 60], 119 points.</t>
+          <t>|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2. Use the Case I calibration from `_ch3_helpers.py`: x1min(y) = y^0.5, c = 0.5, p1 = 1.</t>
+          <t>| **S302-A** (the dataset's single data column) | n/a (theoretical) | Shaikh 2016 eq (3.11), p. 93; Figure 3.4 axis bounds p. 94 | dimensionless | analytic regeneration from equation |</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>3. Evaluate share = (1 - c) * (x1min/y) + c = 0.5 * y^(-0.5) + 0.5.</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4. At y=1 the share is 1.0; it declines monotonically toward c = 0.5 as y -&gt; infinity.</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
@@ -4597,54 +4593,58 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>**Formula**: `p1*x1/y = (1 - c) * (p1*x1min/y) + c`</t>
+          <t>1. Income grid y in [1.0, 60], 119 points.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2. Use the Case I calibration from `_ch3_helpers.py`: x1min(y) = y^0.5, c = 0.5, p1 = 1.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>3. Evaluate share = (1 - c) * (x1min/y) + c = 0.5 * y^(-0.5) + 0.5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4. At y=1 the share is 1.0; it declines monotonically toward c = 0.5 as y -&gt; infinity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>**Formula**: `p1*x1/y = (1 - c) * (p1*x1min/y) + c`</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>- **No year dimension**. The abscissa is a synthetic income grid (model units 1-60).</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>## 6. Units</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-    </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>- **Output**: expenditure share, dimensionless ratio.</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>- **x-axis**: income y in model units.</t>
+          <t>- **No year dimension**. The abscissa is a synthetic income grid (model units 1-60).</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -4664,126 +4664,122 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1. Parameter calibration (x1min(y), c) not stated by Shaikh; we use the same calibration as S301 for internal consistency across the Case I family (S301/S302/S303). Disclosed here and in EPR.</t>
+          <t>- **Output**: expenditure share, dimensionless ratio.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2. Printed Fig 3.4 has y-axis up to 1.2; with our calibration the share at y=1 is 1.0 (within axis). Shaikh's curve approaches the axis maximum at low y; ours does too.</t>
+          <t>- **x-axis**: income y in model units.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>3. No empirical content. No proxy substitution. No synthetic gap-filling.</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>## 7. Caveats</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>## 8. Cross-references</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1. Parameter calibration (x1min(y), c) not stated by Shaikh; we use the same calibration as S301 for internal consistency across the Case I family (S301/S302/S303). Disclosed here and in EPR.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: none</t>
+          <t>2. Printed Fig 3.4 has y-axis up to 1.2; with our calibration the share at y=1 is 1.0 (within axis). Shaikh's curve approaches the axis maximum at low y; ours does too.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 3, Fig3.4 on p. 94</t>
+          <t>3. No empirical content. No proxy substitution. No synthetic gap-filling.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>- **Knowledge Base**: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json` -&gt; Fig3.4</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>## 8. Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>## 9. Validation expectation</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>- **Predecessor series**: none (first constructed in this dataset).</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>- **Tolerance**: PASS_THEORETICAL mode. Checks: monotone declining, asymptote toward c=0.5 at high y, all values within [0.0, 1.2].</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 3, Fig3.4 on p. 94</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>- **Knowledge Base**: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json` -&gt; Fig3.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>- **Source-book text**: Shaikh (2016) Chapter 3, extracted in the project knowledge base (ch03_micro_foundations.md).</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4">
+      <c r="A70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>- **Tolerance**: the validator's theoretical-curve mode (checks the curve's shape and bounds rather than matching tabulated values). Checks: monotone declining, asymptote toward c=0.5 at high y, all values within [0.0, 1.2].</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4">
         <f>== EPR: S302_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t># S302 -- Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>**Series**: S302 -- Expenditure Share of Necessaries, Case I</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>**Content type**: `theoretical`</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>**Related**: `S302_DPR.md`, `Technical/research/S302_research.json`</t>
+          <t># S302 -- Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -4793,27 +4789,35 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Series**: S302 -- Expenditure Share of Necessaries, Case I</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>**Record type**: Extension Provenance Record</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>## 1. Classification</t>
+          <t>**Content type**: `theoretical`</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S302 is a `theoretical` series. It is the share form (eq 3.11) of the same Case I construction as S301. There is no time dimension; no extension applies.</t>
+          <t>**Related**: `S302_DPR.md`, `Technical/research/S302_research.json`</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4827,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>## 2. Method</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4837,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>**Extension method**: `none`. Regenerated from eq (3.11) each loader run.</t>
+          <t>## 1. Classification</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4847,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>## 3. Worked example</t>
+          <t>S302 is a `theoretical` series. It is the share form (eq 3.11) of the same Case I construction as S301. There is no time dimension; no extension applies.</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4857,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Not applicable. Worked example for S302 is the curve itself: at y=1, share = 1.0; at y=60, share = 0.5 + 0.5 * (1/sqrt(60)) approx 0.565. The curve declines monotonically toward c=0.5.</t>
+          <t>## 2. Method</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4867,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>## 4. No-Proxy disclosure</t>
+          <t>**Extension method**: `none`. Regenerated from eq (3.11) each time the data-loading step runs.</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4877,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>No proxy substitution. See `S302_DPR.md` for source details.</t>
+          <t>## 3. Worked example</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4887,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>## 5. No-Synthetic disclosure</t>
+          <t>Not applicable. Worked example for S302 is the curve itself: at y=1, share = 1.0; at y=60, share = 0.5 + 0.5 * (1/sqrt(60)) approx 0.565. The curve declines monotonically toward c=0.5.</t>
         </is>
       </c>
     </row>
@@ -4893,86 +4897,109 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>No synthetic gap-filling in the prohibited sense. The DPR documents any</t>
+          <t>## 4. No-Proxy disclosure</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>analytic regeneration or library-data dependence explicitly.</t>
-        </is>
-      </c>
+      <c r="A100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>No proxy substitution. See `S302_DPR.md` for source details.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>## 5. No-Synthetic disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>No synthetic gap-filling in the prohibited sense. The companion Data Provenance Record (DPR) documents any analytic regeneration or library-data dependence explicitly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>## 6. Failure-mode table</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>Same failure-mode table as S301: calibration choice (x1min, c), bound violation at low y (handled by trimming the grid to y&gt;=1), shape-check failure (would indicate a code bug in `_ch3_helpers.py`).</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>## 7. CD2 divergence pre-disclosure</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>No CD2 predecessor; CD2 comparison block omitted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr"/>
-    </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>## 8. Why no API extension applies</t>
-        </is>
-      </c>
+      <c r="A110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>## 7. Predecessor divergence pre-disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>This series has no time dimension (theoretical/cross_sectional). The</t>
-        </is>
-      </c>
+      <c r="A112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>Predecessor series: none (first constructed in this dataset). The predecessor-comparison block is omitted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>## 8. Why no API extension applies</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>This series has no time dimension (theoretical/cross_sectional). The</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
           <t>Anu-framework rule on extension only applies to `time_series` series. The</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>chopped CSV is the final published deliverable.</t>
         </is>
@@ -5166,7 +5193,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -5335,7 +5362,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-18T22:01:45.649536+00:00</t>
+          <t>2026-07-02T06:22:05.957896+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S302_extenbook.xlsx
+++ b/extenbooks/S302_extenbook.xlsx
@@ -4406,7 +4406,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Status**: theoretical_validated</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-02T06:22:05.957896+00:00</t>
+          <t>2026-07-11T03:44:24.653355+00:00</t>
         </is>
       </c>
     </row>
@@ -5389,11 +5389,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5416,6 +5416,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_2016_EQ_3_4_3_11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>theoretical_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Renderable analytic curve (Shaikh Fig 3.4): the share-of-income form of the Case I necessaries construction, 119 clean points. Renders as an x-y curve over the income grid (carried in the 'year' index column, NOT calendar years). TRIAGE_PRESCREEN had no EMPTY flag for S302 but it shares the index-as-year pattern; L01/P02 exist and replicate.py builds it (PASS). Caveat: agent-chosen Case I calibration (DPR \u00a77) governs levels, not the book; only the shape is faithful. KB coverage: ch03 IS extracted in the book KB (HDARP v3.3 Sraffa OCR campaign) (Body_Text/ch03_micro_foundations.md + Figures/ch03/ch03_fig_3.4.md); the chapter-3 figure quotes in the research JSON ARE verifiable against KB, and a 'From the book' section can be populated in the explainer (doc-side backfill).", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S302_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S302_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Theoretical curve; no historical observations. Calibrated to match the printed axis bounds of the figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>expenditure share (dimensionless ratio)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
